--- a/config/yunying/flop_task.xlsx
+++ b/config/yunying/flop_task.xlsx
@@ -1273,7 +1273,7 @@
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>試練【ハード】に3回挑戦</t>
+          <t>挑战3次考验</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>3回回収</t>
+          <t>三次回收</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>日常ダンジョンを4回クリア</t>
+          <t>日常迷宫通关4次</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>アリーナに5回挑戦</t>
+          <t>5次挑战竞技场</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>スタミナを2回購入</t>
+          <t>购买两次耐力</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>60ダイヤチャージごとに5回完了可能</t>
+          <t>每60颗钻石充值可完成5次</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>60ダイヤチャージごとに10回完了可能</t>
+          <t>每充值60颗钻石可完成10次</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>200ダイヤ消費ごとに3回完了可能</t>
+          <t>每消费200钻可完成3次</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>ノーマルダンジョンを30回クリア</t>
+          <t>完成30次普通地牢</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>アリーナに5回挑戦</t>
+          <t>5次挑战竞技场</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>スタミナを2回購入</t>
+          <t>购买两次耐力</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>60ダイヤチャージするたびに、10回クリアできる</t>
+          <t>每充值60钻可通关10次</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>200ダイヤ消費するたびに、3回クリアできる</t>
+          <t>每消费200钻可通关3次</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>5回回収</t>
+          <t>回收5次</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>ダンジョンを30回クリア</t>
+          <t>完成30次地牢</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>アリーナに5回挑戦</t>
+          <t>5次挑战竞技场</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>スタミナを2回購入</t>
+          <t>购买两次耐力</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>60ダイヤチャージするたびに、10回クリアできる</t>
+          <t>每充值60钻可通关10次</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>200ダイヤ消費するたびに、3回クリアできる</t>
+          <t>每消费200钻可通关3次</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>5回回収</t>
+          <t>回收5次</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>ダンジョンを30回クリア</t>
+          <t>完成30次地牢</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>アリーナに5回挑戦</t>
+          <t>5次挑战竞技场</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>スタミナを2回購入</t>
+          <t>购买两次耐力</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
